--- a/Data_Extraction_Results/LLM_Bias_Data_Extraction.xlsx
+++ b/Data_Extraction_Results/LLM_Bias_Data_Extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\he32\Documents\GitHub\LLM_Assisted_Review_Bias\Data_Extraction_Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079388C4-C627-4A89-A44E-E48BD2D76801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC20D18-59B4-4DF3-B5F0-5EB968D68FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35293" yWindow="-7200" windowWidth="25786" windowHeight="13867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="1191">
   <si>
     <t>title</t>
   </si>
@@ -3523,12 +3523,165 @@
   <si>
     <t>Geriatrics</t>
   </si>
+  <si>
+    <t>GPT-4o mini, GPT-4o, GPT-4, O1-Strawberry (Mini), Claude-3.5 Sonnet, Gemini-1.5 Pro, Gemma-2 (27b), Mistral-Large, Llama 3.1 (405b), Qwen 2.5 (72b)</t>
+  </si>
+  <si>
+    <t>GPT-3.5 , GPT-4.0</t>
+  </si>
+  <si>
+    <t>CHIMED-GPT, GPT-3.5-Turbo, GPT-4, Ziya-v1, Ziya-v2, Barichuan, Taiyi, MedicalGPT (Z), Medical-GPT (B)</t>
+  </si>
+  <si>
+    <t>Copilot, BARD, ChatGPT</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>Copilot, Gemini</t>
+  </si>
+  <si>
+    <t>GPT-3.5</t>
+  </si>
+  <si>
+    <t>GPT-4, Bard, Claude-2</t>
+  </si>
+  <si>
+    <t>GPT-4o, Claude-Sonnet-3.5, Gemini-1.5-Pro</t>
+  </si>
+  <si>
+    <t>GPT-2</t>
+  </si>
+  <si>
+    <t>GPT-3.5, GPT-4</t>
+  </si>
+  <si>
+    <t>GPT-3.5, GPT-4, Claude, Bard</t>
+  </si>
+  <si>
+    <t>GPT-3.5, Gemini, YouChat, Perplexity, Copilot</t>
+  </si>
+  <si>
+    <t>ChatGPT February 13 version</t>
+  </si>
+  <si>
+    <t>GPT-4</t>
+  </si>
+  <si>
+    <t>GPT-4, Bing Chat, Gemini</t>
+  </si>
+  <si>
+    <t>GPT-3.5-Turbo, LLaMA-2-70b-chat, LLaMA-70b-chat</t>
+  </si>
+  <si>
+    <t>Mistral-7B, BioMistral-7B, Mixtral-8x7B, LLaMA-3-8B</t>
+  </si>
+  <si>
+    <t>GPT-3</t>
+  </si>
+  <si>
+    <t>GPT-3.5-turbo</t>
+  </si>
+  <si>
+    <t>Bing Chart, Bard, GPT-3.5</t>
+  </si>
+  <si>
+    <t>GPT-4, Llama-3</t>
+  </si>
+  <si>
+    <t>GPT-3.5-Turbo</t>
+  </si>
+  <si>
+    <t>GPT-4, ChatGPT, Qwen1.5-52B</t>
+  </si>
+  <si>
+    <t>GPT-3.5-Turbo, GPT-4-Turbo, GPT-4o, Gemini-1.5-Flash, Llama3-8B</t>
+  </si>
+  <si>
+    <t>LLaMA-13B</t>
+  </si>
+  <si>
+    <t>GPT-4-Turbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-3.5, GPT-4, Llama-2 </t>
+  </si>
+  <si>
+    <t>GPT-4, PaLM-2</t>
+  </si>
+  <si>
+    <t>GPT-3.5, GPT-4, Flan-T5</t>
+  </si>
+  <si>
+    <t>GPT-3.5, , Gemini, Copilot</t>
+  </si>
+  <si>
+    <t>ChatGPT-4, Gemini 1.5 Flash, Bing Chat</t>
+  </si>
+  <si>
+    <t>GPT-3.5-Turbo, GPT-4-Turbo-Preview</t>
+  </si>
+  <si>
+    <t>Med-PaLM, Flan-PaLM</t>
+  </si>
+  <si>
+    <t>ChatGPT (January 30th version)</t>
+  </si>
+  <si>
+    <t>GPT-3.5, GPT-4, Bing, Bard</t>
+  </si>
+  <si>
+    <t>GPT3.5-Turbo</t>
+  </si>
+  <si>
+    <t>GPT-3.5, Gemini</t>
+  </si>
+  <si>
+    <t>GPT-4, LLaMA-3</t>
+  </si>
+  <si>
+    <t>GPT-3.5 , GPT-4</t>
+  </si>
+  <si>
+    <t>GPT-3.5-turbo, GPT-4, Gemini-1.0-pro, Llama3-70b</t>
+  </si>
+  <si>
+    <t>Med-PaLM2</t>
+  </si>
+  <si>
+    <t>GPT-3.5-Turbo, GPT-4</t>
+  </si>
+  <si>
+    <t>GPT-4, GPT-3.5, Mental-LLaMa</t>
+  </si>
+  <si>
+    <t>ASCLEPIUS-7B, CLINICAL-CAMEL-13B, MEDALPACA-7B, LLAMA2-CHAT-7B, LLAMA2-CHAT-13B, ALPACA-7B, MISTRAL-IT-0.2-7B</t>
+  </si>
+  <si>
+    <t>BERT, PubMedBERT, RoBERTa, AlBERT, Bart, BioBART, GPT-2, BioGPT, LLaMa2-7b, LLaMa2-13b, BioMedGPT</t>
+  </si>
+  <si>
+    <t>GPT-4, Gemini</t>
+  </si>
+  <si>
+    <t>GPT-4, Claude-3, LLaMA-3</t>
+  </si>
+  <si>
+    <t>GPT-4, MentaLLaMA</t>
+  </si>
+  <si>
+    <t>Bard, Bing, GPT-3.5</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3596,6 +3749,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -3643,7 +3802,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3668,6 +3827,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3950,38 +4111,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB81"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC81"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="57.5546875" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" customWidth="1"/>
-    <col min="4" max="4" width="39.44140625" customWidth="1"/>
+    <col min="1" max="1" width="57.53125" customWidth="1"/>
+    <col min="2" max="2" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="39.46484375" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="49.44140625" customWidth="1"/>
+    <col min="6" max="6" width="49.46484375" customWidth="1"/>
     <col min="7" max="7" width="39.33203125" customWidth="1"/>
-    <col min="8" max="8" width="49.77734375" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="49.796875" customWidth="1"/>
+    <col min="9" max="9" width="15.86328125" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.88671875" customWidth="1"/>
-    <col min="14" max="14" width="45.21875" customWidth="1"/>
-    <col min="15" max="15" width="23.109375" customWidth="1"/>
-    <col min="16" max="16" width="49.5546875" customWidth="1"/>
-    <col min="17" max="17" width="19.5546875" customWidth="1"/>
-    <col min="18" max="18" width="21.6640625" customWidth="1"/>
-    <col min="19" max="19" width="15.21875" customWidth="1"/>
-    <col min="20" max="20" width="41.44140625" customWidth="1"/>
-    <col min="21" max="21" width="14.6640625" customWidth="1"/>
-    <col min="22" max="22" width="51.5546875" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="40.21875" customWidth="1"/>
-    <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="25" width="22.33203125" customWidth="1"/>
-    <col min="26" max="26" width="48.44140625" customWidth="1"/>
-    <col min="27" max="27" width="19.77734375" customWidth="1"/>
-    <col min="28" max="28" width="28.109375" customWidth="1"/>
+    <col min="11" max="11" width="45.1328125" customWidth="1"/>
+    <col min="13" max="13" width="13.53125" customWidth="1"/>
+    <col min="14" max="14" width="14.86328125" customWidth="1"/>
+    <col min="15" max="15" width="45.19921875" customWidth="1"/>
+    <col min="16" max="16" width="23.1328125" customWidth="1"/>
+    <col min="17" max="17" width="49.53125" customWidth="1"/>
+    <col min="18" max="18" width="19.53125" customWidth="1"/>
+    <col min="19" max="19" width="21.6640625" customWidth="1"/>
+    <col min="20" max="20" width="15.19921875" customWidth="1"/>
+    <col min="21" max="21" width="41.46484375" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" customWidth="1"/>
+    <col min="23" max="23" width="51.53125" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="40.19921875" customWidth="1"/>
+    <col min="25" max="25" width="21" customWidth="1"/>
+    <col min="26" max="26" width="22.33203125" customWidth="1"/>
+    <col min="27" max="27" width="48.46484375" customWidth="1"/>
+    <col min="28" max="28" width="19.796875" customWidth="1"/>
+    <col min="29" max="29" width="28.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="28.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="28.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4012,62 +4174,65 @@
       <c r="J1" s="3" t="s">
         <v>1118</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="16" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>1119</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>1121</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>1123</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>1124</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>1125</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="7" t="s">
         <v>1127</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="V1" s="7" t="s">
         <v>1128</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>467</v>
       </c>
@@ -4098,62 +4263,65 @@
       <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>452</v>
       </c>
@@ -4184,62 +4352,65 @@
       <c r="J3" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="10" t="s">
+      <c r="X3" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>160</v>
       </c>
@@ -4270,60 +4441,63 @@
       <c r="J4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="10" t="s">
+      <c r="W4" s="2"/>
+      <c r="X4" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>603</v>
       </c>
@@ -4354,60 +4528,63 @@
       <c r="J5" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V5" s="2"/>
-      <c r="W5" s="10" t="s">
+      <c r="W5" s="2"/>
+      <c r="X5" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="AA5" s="2" t="s">
+      <c r="AB5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB5" s="2" t="s">
+      <c r="AC5" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>220</v>
       </c>
@@ -4438,60 +4615,63 @@
       <c r="J6" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="T6" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2" t="s">
+      <c r="W6" s="2"/>
+      <c r="X6" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA6" s="2" t="s">
+      <c r="AB6" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>585</v>
       </c>
@@ -4522,60 +4702,63 @@
       <c r="J7" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2" t="s">
+      <c r="W7" s="2"/>
+      <c r="X7" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="AA7" s="11" t="s">
+      <c r="AB7" s="11" t="s">
         <v>725</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>562</v>
       </c>
@@ -4606,60 +4789,63 @@
       <c r="J8" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2" t="s">
+      <c r="W8" s="2"/>
+      <c r="X8" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>554</v>
       </c>
@@ -4690,60 +4876,63 @@
       <c r="J9" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="2"/>
+      <c r="X9" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AC9" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>252</v>
       </c>
@@ -4774,60 +4963,63 @@
       <c r="J10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="U10" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="2"/>
+      <c r="X10" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AB10" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="13.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>401</v>
       </c>
@@ -4858,62 +5050,65 @@
       <c r="J11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" t="s">
+        <v>1148</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="U11" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U11" s="9" t="s">
+      <c r="V11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="X11" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="Z11" s="12" t="s">
+      <c r="AA11" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="AA11" s="2" t="s">
+      <c r="AB11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB11" s="2" t="s">
+      <c r="AC11" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="17.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>184</v>
       </c>
@@ -4944,60 +5139,63 @@
       <c r="J12" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="U12" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2" t="s">
+      <c r="W12" s="2"/>
+      <c r="X12" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y12" s="2" t="s">
+      <c r="Z12" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="Z12" s="2" t="s">
+      <c r="AA12" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="AA12" s="2" t="s">
+      <c r="AB12" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="AB12" s="2" t="s">
+      <c r="AC12" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>317</v>
       </c>
@@ -5028,60 +5226,63 @@
       <c r="J13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="U13" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="2"/>
-      <c r="W13" s="10" t="s">
+      <c r="W13" s="2"/>
+      <c r="X13" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X13" s="2" t="s">
+      <c r="Y13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y13" s="2" t="s">
+      <c r="Z13" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="Z13" s="9" t="s">
+      <c r="AA13" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="AA13" s="2" t="s">
+      <c r="AB13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB13" s="2" t="s">
+      <c r="AC13" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>308</v>
       </c>
@@ -5112,60 +5313,63 @@
       <c r="J14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="U14" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2" t="s">
+      <c r="W14" s="2"/>
+      <c r="X14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="2" t="s">
+      <c r="Y14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y14" s="2" t="s">
+      <c r="Z14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z14" s="2" t="s">
+      <c r="AA14" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AA14" s="2" t="s">
+      <c r="AB14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB14" s="2" t="s">
+      <c r="AC14" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>55</v>
       </c>
@@ -5196,62 +5400,65 @@
       <c r="J15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="U15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="W15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="X15" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X15" s="2" t="s">
+      <c r="Y15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y15" s="2" t="s">
+      <c r="Z15" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z15" s="2" t="s">
+      <c r="AA15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AA15" s="2" t="s">
+      <c r="AB15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB15" s="2" t="s">
+      <c r="AC15" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>93</v>
       </c>
@@ -5282,60 +5489,63 @@
       <c r="J16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="U16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="V16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2" t="s">
+      <c r="W16" s="2"/>
+      <c r="X16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="X16" s="2" t="s">
+      <c r="Y16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y16" s="2" t="s">
+      <c r="Z16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Z16" s="2" t="s">
+      <c r="AA16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AA16" s="2" t="s">
+      <c r="AB16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB16" s="2" t="s">
+      <c r="AC16" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>368</v>
       </c>
@@ -5366,62 +5576,65 @@
       <c r="J17" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="U17" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="U17" s="9" t="s">
+      <c r="V17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="W17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W17" s="10" t="s">
+      <c r="X17" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X17" s="2" t="s">
+      <c r="Y17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y17" s="2" t="s">
+      <c r="Z17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z17" s="2" t="s">
+      <c r="AA17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA17" s="2" t="s">
+      <c r="AB17" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="AB17" s="2" t="s">
+      <c r="AC17" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>594</v>
       </c>
@@ -5452,60 +5665,63 @@
       <c r="J18" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="U18" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V18" s="2"/>
-      <c r="W18" s="10" t="s">
+      <c r="W18" s="2"/>
+      <c r="X18" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X18" s="2" t="s">
+      <c r="Y18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y18" s="2" t="s">
+      <c r="Z18" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="Z18" s="2" t="s">
+      <c r="AA18" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="AA18" s="2" t="s">
+      <c r="AB18" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="AB18" s="2" t="s">
+      <c r="AC18" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>483</v>
       </c>
@@ -5536,62 +5752,65 @@
       <c r="J19" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="U19" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="U19" s="9" t="s">
+      <c r="V19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V19" s="2" t="s">
+      <c r="W19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W19" s="10" t="s">
+      <c r="X19" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X19" s="2" t="s">
+      <c r="Y19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y19" s="2" t="s">
+      <c r="Z19" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="Z19" s="2" t="s">
+      <c r="AA19" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="AA19" s="2" t="s">
+      <c r="AB19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB19" s="2" t="s">
+      <c r="AC19" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>533</v>
       </c>
@@ -5622,60 +5841,63 @@
       <c r="J20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="U20" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="V20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2" t="s">
+      <c r="W20" s="2"/>
+      <c r="X20" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X20" s="2" t="s">
+      <c r="Y20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y20" s="2" t="s">
+      <c r="Z20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z20" s="2" t="s">
+      <c r="AA20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA20" s="2" t="s">
+      <c r="AB20" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="AB20" s="2" t="s">
+      <c r="AC20" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>45</v>
       </c>
@@ -5706,60 +5928,63 @@
       <c r="J21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="S21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="T21" s="2" t="s">
+      <c r="U21" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="V21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2" t="s">
+      <c r="W21" s="2"/>
+      <c r="X21" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="X21" s="2" t="s">
+      <c r="Y21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y21" s="2" t="s">
+      <c r="Z21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Z21" s="2" t="s">
+      <c r="AA21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AA21" s="2" t="s">
+      <c r="AB21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB21" s="2" t="s">
+      <c r="AC21" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>74</v>
       </c>
@@ -5790,60 +6015,63 @@
       <c r="J22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="U22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="V22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V22" s="2"/>
-      <c r="W22" s="10" t="s">
+      <c r="W22" s="2"/>
+      <c r="X22" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="X22" s="2" t="s">
+      <c r="Y22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y22" s="2" t="s">
+      <c r="Z22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z22" s="2" t="s">
+      <c r="AA22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA22" s="2" t="s">
+      <c r="AB22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AB22" s="2" t="s">
+      <c r="AC22" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>176</v>
       </c>
@@ -5872,60 +6100,63 @@
       <c r="J23" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="S23" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="U23" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2" t="s">
+      <c r="W23" s="2"/>
+      <c r="X23" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X23" s="2" t="s">
+      <c r="Y23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y23" s="2" t="s">
+      <c r="Z23" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="Z23" s="2" t="s">
+      <c r="AA23" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AA23" s="2" t="s">
+      <c r="AB23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB23" s="2" t="s">
+      <c r="AC23" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>124</v>
       </c>
@@ -5954,60 +6185,63 @@
       <c r="J24" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" t="s">
+        <v>1157</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="S24" s="2" t="s">
+      <c r="T24" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="U24" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="V24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2" t="s">
+      <c r="W24" s="2"/>
+      <c r="X24" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X24" s="2" t="s">
+      <c r="Y24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y24" s="2" t="s">
+      <c r="Z24" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="Z24" s="2" t="s">
+      <c r="AA24" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="AA24" s="2" t="s">
+      <c r="AB24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB24" s="2" t="s">
+      <c r="AC24" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>259</v>
       </c>
@@ -6038,60 +6272,63 @@
       <c r="J25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" t="s">
+        <v>1158</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="T25" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="T25" s="2" t="s">
+      <c r="U25" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U25" s="2" t="s">
+      <c r="V25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V25" s="2"/>
-      <c r="W25" s="10" t="s">
+      <c r="W25" s="2"/>
+      <c r="X25" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X25" s="2" t="s">
+      <c r="Y25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y25" s="2" t="s">
+      <c r="Z25" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="Z25" s="2" t="s">
+      <c r="AA25" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="AA25" s="2" t="s">
+      <c r="AB25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB25" s="2" t="s">
+      <c r="AC25" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="20.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>213</v>
       </c>
@@ -6122,58 +6359,61 @@
       <c r="J26" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K26" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R26" s="2" t="s">
+      <c r="S26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S26" s="2" t="s">
+      <c r="T26" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="T26" s="2" t="s">
+      <c r="U26" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U26" s="2" t="s">
+      <c r="V26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V26" s="2"/>
-      <c r="W26" s="10" t="s">
+      <c r="W26" s="2"/>
+      <c r="X26" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X26" s="2" t="s">
+      <c r="Y26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y26" s="2" t="s">
+      <c r="Z26" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Z26" s="2" t="s">
+      <c r="AA26" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2" t="s">
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>101</v>
       </c>
@@ -6204,60 +6444,63 @@
       <c r="J27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="M27" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R27" s="2" t="s">
+      <c r="S27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="S27" s="2" t="s">
+      <c r="T27" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T27" s="2" t="s">
+      <c r="U27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="V27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V27" s="2"/>
-      <c r="W27" s="10" t="s">
+      <c r="W27" s="2"/>
+      <c r="X27" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X27" s="2" t="s">
+      <c r="Y27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y27" s="2" t="s">
+      <c r="Z27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z27" s="2" t="s">
+      <c r="AA27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA27" s="2" t="s">
+      <c r="AB27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AB27" s="2" t="s">
+      <c r="AC27" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>350</v>
       </c>
@@ -6288,60 +6531,63 @@
       <c r="J28" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="O28" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R28" s="2" t="s">
+      <c r="S28" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="T28" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="T28" s="2" t="s">
+      <c r="U28" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="V28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="2"/>
+      <c r="X28" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="X28" s="2" t="s">
+      <c r="Y28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y28" s="2" t="s">
+      <c r="Z28" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="Z28" s="2" t="s">
+      <c r="AA28" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="AA28" s="2" t="s">
+      <c r="AB28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB28" s="2" t="s">
+      <c r="AC28" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>360</v>
       </c>
@@ -6372,60 +6618,63 @@
       <c r="J29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="K29" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R29" s="2" t="s">
+      <c r="S29" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="T29" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="T29" s="2" t="s">
+      <c r="U29" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="V29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V29" s="2"/>
-      <c r="W29" s="10" t="s">
+      <c r="W29" s="2"/>
+      <c r="X29" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="X29" s="2" t="s">
+      <c r="Y29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y29" s="2" t="s">
+      <c r="Z29" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z29" s="2" t="s">
+      <c r="AA29" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="AA29" s="11" t="s">
+      <c r="AB29" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="AB29" s="2" t="s">
+      <c r="AC29" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>238</v>
       </c>
@@ -6456,60 +6705,63 @@
       <c r="J30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="S30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="T30" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="T30" s="2" t="s">
+      <c r="U30" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="V30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V30" s="2"/>
-      <c r="W30" s="10" t="s">
+      <c r="W30" s="2"/>
+      <c r="X30" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X30" s="2" t="s">
+      <c r="Y30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y30" s="2" t="s">
+      <c r="Z30" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Z30" s="2" t="s">
+      <c r="AA30" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="AA30" s="2" t="s">
+      <c r="AB30" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB30" s="2" t="s">
+      <c r="AC30" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>337</v>
       </c>
@@ -6540,60 +6792,63 @@
       <c r="J31" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="K31" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R31" s="2" t="s">
+      <c r="S31" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="S31" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="T31" s="2" t="s">
+      <c r="U31" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="V31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V31" s="2"/>
-      <c r="W31" s="10" t="s">
+      <c r="W31" s="2"/>
+      <c r="X31" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X31" s="2" t="s">
+      <c r="Y31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y31" s="2" t="s">
+      <c r="Z31" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z31" s="2" t="s">
+      <c r="AA31" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="AA31" s="2" t="s">
+      <c r="AB31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB31" s="2" t="s">
+      <c r="AC31" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>152</v>
       </c>
@@ -6622,60 +6877,63 @@
       <c r="J32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="Q32" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="R32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R32" s="2" t="s">
+      <c r="S32" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="S32" s="2" t="s">
+      <c r="T32" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="U32" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="V32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2" t="s">
+      <c r="W32" s="2"/>
+      <c r="X32" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="X32" s="2" t="s">
+      <c r="Y32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y32" s="2" t="s">
+      <c r="Z32" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="Z32" s="2" t="s">
+      <c r="AA32" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="AA32" s="2" t="s">
+      <c r="AB32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB32" s="2" t="s">
+      <c r="AC32" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>141</v>
       </c>
@@ -6704,60 +6962,63 @@
       <c r="J33" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K33" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="O33" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="Q33" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="R33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R33" s="2" t="s">
+      <c r="S33" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S33" s="2" t="s">
+      <c r="T33" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="U33" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="V33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V33" s="2"/>
-      <c r="W33" s="10" t="s">
+      <c r="W33" s="2"/>
+      <c r="X33" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X33" s="2" t="s">
+      <c r="Y33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y33" s="2" t="s">
+      <c r="Z33" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="Z33" s="2" t="s">
+      <c r="AA33" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AA33" s="2" t="s">
+      <c r="AB33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB33" s="2" t="s">
+      <c r="AC33" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>514</v>
       </c>
@@ -6788,62 +7049,65 @@
       <c r="J34" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="Q34" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="R34" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="R34" s="2" t="s">
+      <c r="S34" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="S34" s="2" t="s">
+      <c r="T34" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="U34" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="U34" s="9" t="s">
+      <c r="V34" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V34" s="2" t="s">
+      <c r="W34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W34" s="10" t="s">
+      <c r="X34" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X34" s="2" t="s">
+      <c r="Y34" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y34" s="2" t="s">
+      <c r="Z34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z34" s="2" t="s">
+      <c r="AA34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA34" s="2" t="s">
+      <c r="AB34" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="AB34" s="2" t="s">
+      <c r="AC34" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>568</v>
       </c>
@@ -6874,60 +7138,63 @@
       <c r="J35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" t="s">
+        <v>1166</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="Q35" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="R35" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R35" s="2" t="s">
+      <c r="S35" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S35" s="2" t="s">
+      <c r="T35" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="T35" s="2" t="s">
+      <c r="U35" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="U35" s="2" t="s">
+      <c r="V35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V35" s="2"/>
-      <c r="W35" s="10" t="s">
+      <c r="W35" s="2"/>
+      <c r="X35" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X35" s="2" t="s">
+      <c r="Y35" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y35" s="2" t="s">
+      <c r="Z35" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="Z35" s="2" t="s">
+      <c r="AA35" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="AA35" s="2" t="s">
+      <c r="AB35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB35" s="2" t="s">
+      <c r="AC35" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>521</v>
       </c>
@@ -6958,62 +7225,65 @@
       <c r="J36" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" t="s">
+        <v>1167</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="P36" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="Q36" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="R36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R36" s="2" t="s">
+      <c r="S36" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="T36" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="U36" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="U36" s="9" t="s">
+      <c r="V36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V36" s="2" t="s">
+      <c r="W36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W36" s="10" t="s">
+      <c r="X36" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X36" s="2" t="s">
+      <c r="Y36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y36" s="2" t="s">
+      <c r="Z36" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z36" s="9" t="s">
+      <c r="AA36" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="AA36" s="2" t="s">
+      <c r="AB36" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="AB36" s="2" t="s">
+      <c r="AC36" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>423</v>
       </c>
@@ -7044,62 +7314,65 @@
       <c r="J37" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K37" t="s">
+        <v>1168</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="P37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="Q37" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R37" s="2" t="s">
+      <c r="S37" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="S37" s="2" t="s">
+      <c r="T37" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="T37" s="2" t="s">
+      <c r="U37" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="U37" s="9" t="s">
+      <c r="V37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V37" s="2" t="s">
+      <c r="W37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W37" s="10" t="s">
+      <c r="X37" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X37" s="2" t="s">
+      <c r="Y37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y37" s="2" t="s">
+      <c r="Z37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z37" s="2" t="s">
+      <c r="AA37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA37" s="2" t="s">
+      <c r="AB37" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="AB37" s="2" t="s">
+      <c r="AC37" s="2" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>290</v>
       </c>
@@ -7130,60 +7403,63 @@
       <c r="J38" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="K38" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="R38" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="S38" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="S38" s="2" t="s">
+      <c r="T38" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="T38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U38" s="2" t="s">
+      <c r="V38" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V38" s="2"/>
-      <c r="W38" s="2" t="s">
+      <c r="W38" s="2"/>
+      <c r="X38" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X38" s="2" t="s">
+      <c r="Y38" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y38" s="2" t="s">
+      <c r="Z38" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="Z38" s="2" t="s">
+      <c r="AA38" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AA38" s="2" t="s">
+      <c r="AB38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB38" s="2" t="s">
+      <c r="AC38" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>168</v>
       </c>
@@ -7214,60 +7490,63 @@
       <c r="J39" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="K39" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="P39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P39" s="2" t="s">
+      <c r="Q39" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="R39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R39" s="2" t="s">
+      <c r="S39" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="S39" s="2" t="s">
+      <c r="T39" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="T39" s="2" t="s">
+      <c r="U39" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U39" s="2" t="s">
+      <c r="V39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V39" s="2"/>
-      <c r="W39" s="2" t="s">
+      <c r="W39" s="2"/>
+      <c r="X39" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X39" s="2" t="s">
+      <c r="Y39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y39" s="2" t="s">
+      <c r="Z39" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="Z39" s="2" t="s">
+      <c r="AA39" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AA39" s="2" t="s">
+      <c r="AB39" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB39" s="2" t="s">
+      <c r="AC39" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>283</v>
       </c>
@@ -7298,58 +7577,61 @@
       <c r="J40" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="K40" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="O40" s="2" t="s">
+      <c r="P40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P40" s="2" t="s">
+      <c r="Q40" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="Q40" s="2" t="s">
+      <c r="R40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R40" s="2" t="s">
+      <c r="S40" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S40" s="2" t="s">
+      <c r="T40" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="T40" s="2" t="s">
+      <c r="U40" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U40" s="2" t="s">
+      <c r="V40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V40" s="2"/>
-      <c r="W40" s="2" t="s">
+      <c r="W40" s="2"/>
+      <c r="X40" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="X40" s="2" t="s">
+      <c r="Y40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y40" s="2" t="s">
+      <c r="Z40" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z40" s="2" t="s">
+      <c r="AA40" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AA40" s="2"/>
-      <c r="AB40" s="2" t="s">
+      <c r="AB40" s="2"/>
+      <c r="AC40" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>415</v>
       </c>
@@ -7380,62 +7662,65 @@
       <c r="J41" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="K41" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="O41" s="2" t="s">
+      <c r="P41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P41" s="2" t="s">
+      <c r="Q41" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="Q41" s="2" t="s">
+      <c r="R41" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R41" s="2" t="s">
+      <c r="S41" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="S41" s="2" t="s">
+      <c r="T41" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="T41" s="2" t="s">
+      <c r="U41" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="U41" s="9" t="s">
+      <c r="V41" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V41" s="2" t="s">
+      <c r="W41" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W41" s="2" t="s">
+      <c r="X41" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="X41" s="2" t="s">
+      <c r="Y41" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y41" s="2" t="s">
+      <c r="Z41" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="Z41" s="2" t="s">
+      <c r="AA41" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="AA41" s="2" t="s">
+      <c r="AB41" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB41" s="2" t="s">
+      <c r="AC41" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>577</v>
       </c>
@@ -7466,60 +7751,63 @@
       <c r="J42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K42" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="O42" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="O42" s="2" t="s">
+      <c r="P42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P42" s="2" t="s">
+      <c r="Q42" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="Q42" s="2" t="s">
+      <c r="R42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R42" s="2" t="s">
+      <c r="S42" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S42" s="2" t="s">
+      <c r="T42" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="T42" s="2" t="s">
+      <c r="U42" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="U42" s="2" t="s">
+      <c r="V42" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V42" s="2"/>
-      <c r="W42" s="2" t="s">
+      <c r="W42" s="2"/>
+      <c r="X42" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X42" s="2" t="s">
+      <c r="Y42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y42" s="2" t="s">
+      <c r="Z42" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z42" s="2" t="s">
+      <c r="AA42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA42" s="2" t="s">
+      <c r="AB42" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="AB42" s="2" t="s">
+      <c r="AC42" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>198</v>
       </c>
@@ -7550,60 +7838,63 @@
       <c r="J43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K43" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="O43" s="2" t="s">
+      <c r="P43" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="P43" s="2" t="s">
+      <c r="Q43" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="R43" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R43" s="2" t="s">
+      <c r="S43" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="S43" s="2" t="s">
+      <c r="T43" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="T43" s="2" t="s">
+      <c r="U43" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="U43" s="2" t="s">
+      <c r="V43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V43" s="2"/>
-      <c r="W43" s="2" t="s">
+      <c r="W43" s="2"/>
+      <c r="X43" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="X43" s="2" t="s">
+      <c r="Y43" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y43" s="2" t="s">
+      <c r="Z43" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="Z43" s="2" t="s">
+      <c r="AA43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="AA43" s="2" t="s">
+      <c r="AB43" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB43" s="2" t="s">
+      <c r="AC43" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>245</v>
       </c>
@@ -7634,60 +7925,63 @@
       <c r="J44" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="K44" t="s">
+        <v>1173</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="P44" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="P44" s="2" t="s">
+      <c r="Q44" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="Q44" s="2" t="s">
+      <c r="R44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R44" s="2" t="s">
+      <c r="S44" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="S44" s="2" t="s">
+      <c r="T44" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="T44" s="2" t="s">
+      <c r="U44" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="U44" s="2" t="s">
+      <c r="V44" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V44" s="2"/>
-      <c r="W44" s="2" t="s">
+      <c r="W44" s="2"/>
+      <c r="X44" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="X44" s="2" t="s">
+      <c r="Y44" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y44" s="2" t="s">
+      <c r="Z44" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="Z44" s="2" t="s">
+      <c r="AA44" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="AA44" s="2" t="s">
+      <c r="AB44" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="AB44" s="2" t="s">
+      <c r="AC44" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>499</v>
       </c>
@@ -7718,62 +8012,65 @@
       <c r="J45" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K45" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="O45" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="O45" s="2" t="s">
+      <c r="P45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P45" s="2" t="s">
+      <c r="Q45" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="Q45" s="2" t="s">
+      <c r="R45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R45" s="2" t="s">
+      <c r="S45" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="S45" s="2" t="s">
+      <c r="T45" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="T45" s="2" t="s">
+      <c r="U45" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="U45" s="9" t="s">
+      <c r="V45" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V45" s="2" t="s">
+      <c r="W45" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W45" s="2" t="s">
+      <c r="X45" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X45" s="2" t="s">
+      <c r="Y45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y45" s="2" t="s">
+      <c r="Z45" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z45" s="2" t="s">
+      <c r="AA45" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="AA45" s="2" t="s">
+      <c r="AB45" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB45" s="2" t="s">
+      <c r="AC45" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>378</v>
       </c>
@@ -7804,62 +8101,65 @@
       <c r="J46" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="K46" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="Q46" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="R46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R46" s="2" t="s">
+      <c r="S46" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="S46" s="2" t="s">
+      <c r="T46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T46" s="2" t="s">
+      <c r="U46" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="U46" s="9" t="s">
+      <c r="V46" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V46" s="2" t="s">
+      <c r="W46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W46" s="10" t="s">
+      <c r="X46" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="X46" s="2" t="s">
+      <c r="Y46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y46" s="2" t="s">
+      <c r="Z46" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="Z46" s="2" t="s">
+      <c r="AA46" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="AA46" s="2" t="s">
+      <c r="AB46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB46" s="2" t="s">
+      <c r="AC46" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>435</v>
       </c>
@@ -7890,62 +8190,65 @@
       <c r="J47" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="K47" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="O47" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="O47" s="2" t="s">
+      <c r="P47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P47" s="2" t="s">
+      <c r="Q47" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="Q47" s="2" t="s">
+      <c r="R47" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R47" s="2" t="s">
+      <c r="S47" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="S47" s="2" t="s">
+      <c r="T47" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="T47" s="2" t="s">
+      <c r="U47" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="U47" s="9" t="s">
+      <c r="V47" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V47" s="2" t="s">
+      <c r="W47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W47" s="10" t="s">
+      <c r="X47" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="X47" s="2" t="s">
+      <c r="Y47" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y47" s="2" t="s">
+      <c r="Z47" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z47" s="2" t="s">
+      <c r="AA47" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="AA47" s="2" t="s">
+      <c r="AB47" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB47" s="2" t="s">
+      <c r="AC47" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>541</v>
       </c>
@@ -7976,60 +8279,63 @@
       <c r="J48" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K48" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="O48" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="P48" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P48" s="2" t="s">
+      <c r="Q48" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="Q48" s="2" t="s">
+      <c r="R48" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R48" s="2" t="s">
+      <c r="S48" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S48" s="2" t="s">
+      <c r="T48" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="T48" s="2" t="s">
+      <c r="U48" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="V48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V48" s="2"/>
-      <c r="W48" s="10" t="s">
+      <c r="W48" s="2"/>
+      <c r="X48" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="X48" s="2" t="s">
+      <c r="Y48" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y48" s="2" t="s">
+      <c r="Z48" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="Z48" s="2" t="s">
+      <c r="AA48" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="AA48" s="2" t="s">
+      <c r="AB48" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB48" s="2" t="s">
+      <c r="AC48" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>547</v>
       </c>
@@ -8060,60 +8366,63 @@
       <c r="J49" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K49" t="s">
+        <v>1176</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="O49" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="O49" s="2" t="s">
+      <c r="P49" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="P49" s="2" t="s">
+      <c r="Q49" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="Q49" s="2" t="s">
+      <c r="R49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R49" s="2" t="s">
+      <c r="S49" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="T49" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="T49" s="2" t="s">
+      <c r="U49" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="U49" s="2" t="s">
+      <c r="V49" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V49" s="2"/>
-      <c r="W49" s="10" t="s">
+      <c r="W49" s="2"/>
+      <c r="X49" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="X49" s="2" t="s">
+      <c r="Y49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y49" s="2" t="s">
+      <c r="Z49" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Z49" s="2" t="s">
+      <c r="AA49" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="AA49" s="2" t="s">
+      <c r="AB49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB49" s="2" t="s">
+      <c r="AC49" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>324</v>
       </c>
@@ -8144,60 +8453,63 @@
       <c r="J50" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K50" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="N50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="O50" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O50" s="2" t="s">
+      <c r="P50" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P50" s="2" t="s">
+      <c r="Q50" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="Q50" s="2" t="s">
+      <c r="R50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R50" s="2" t="s">
+      <c r="S50" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S50" s="2" t="s">
+      <c r="T50" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="T50" s="2" t="s">
+      <c r="U50" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="U50" s="2" t="s">
+      <c r="V50" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V50" s="2"/>
-      <c r="W50" s="10" t="s">
+      <c r="W50" s="2"/>
+      <c r="X50" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="X50" s="2" t="s">
+      <c r="Y50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y50" s="2" t="s">
+      <c r="Z50" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z50" s="2" t="s">
+      <c r="AA50" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="AA50" s="2" t="s">
+      <c r="AB50" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB50" s="2" t="s">
+      <c r="AC50" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>386</v>
       </c>
@@ -8226,62 +8538,65 @@
       <c r="J51" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K51" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L51" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="M51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="N51" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N51" s="2" t="s">
+      <c r="O51" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="O51" s="2" t="s">
+      <c r="P51" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P51" s="2" t="s">
+      <c r="Q51" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="Q51" s="2" t="s">
+      <c r="R51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R51" s="2" t="s">
+      <c r="S51" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="S51" s="2" t="s">
+      <c r="T51" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="T51" s="2" t="s">
+      <c r="U51" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="U51" s="9" t="s">
+      <c r="V51" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V51" s="2" t="s">
+      <c r="W51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W51" s="2" t="s">
+      <c r="X51" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X51" s="2" t="s">
+      <c r="Y51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y51" s="2" t="s">
+      <c r="Z51" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Z51" s="2" t="s">
+      <c r="AA51" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="AA51" s="2" t="s">
+      <c r="AB51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB51" s="2" t="s">
+      <c r="AC51" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>458</v>
       </c>
@@ -8312,62 +8627,65 @@
       <c r="J52" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K52" t="s">
+        <v>1177</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="N52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N52" s="2" t="s">
+      <c r="O52" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="O52" s="2" t="s">
+      <c r="P52" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P52" s="2" t="s">
+      <c r="Q52" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="Q52" s="2" t="s">
+      <c r="R52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R52" s="2" t="s">
+      <c r="S52" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="S52" s="2" t="s">
+      <c r="T52" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="T52" s="2" t="s">
+      <c r="U52" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="U52" s="9" t="s">
+      <c r="V52" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V52" s="2" t="s">
+      <c r="W52" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W52" s="2" t="s">
+      <c r="X52" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="X52" s="2" t="s">
+      <c r="Y52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y52" s="2" t="s">
+      <c r="Z52" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="Z52" s="2" t="s">
+      <c r="AA52" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="AA52" s="2" t="s">
+      <c r="AB52" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB52" s="2" t="s">
+      <c r="AC52" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>394</v>
       </c>
@@ -8398,62 +8716,65 @@
       <c r="J53" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="K53" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L53" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="N53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="O53" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O53" s="2" t="s">
+      <c r="P53" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P53" s="2" t="s">
+      <c r="Q53" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="Q53" s="2" t="s">
+      <c r="R53" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="R53" s="2" t="s">
+      <c r="S53" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="S53" s="2" t="s">
+      <c r="T53" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="T53" s="2" t="s">
+      <c r="U53" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="U53" s="9" t="s">
+      <c r="V53" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V53" s="2" t="s">
+      <c r="W53" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W53" s="2" t="s">
+      <c r="X53" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X53" s="2" t="s">
+      <c r="Y53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y53" s="2" t="s">
+      <c r="Z53" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z53" s="2" t="s">
+      <c r="AA53" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="AA53" s="2" t="s">
+      <c r="AB53" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB53" s="2" t="s">
+      <c r="AC53" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>507</v>
       </c>
@@ -8484,62 +8805,65 @@
       <c r="J54" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="K54" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="M54" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="O54" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="O54" s="2" t="s">
+      <c r="P54" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="Q54" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="Q54" s="2" t="s">
+      <c r="R54" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R54" s="2" t="s">
+      <c r="S54" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="S54" s="2" t="s">
+      <c r="T54" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="T54" s="2" t="s">
+      <c r="U54" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="U54" s="9" t="s">
+      <c r="V54" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V54" s="2" t="s">
+      <c r="W54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W54" s="10" t="s">
+      <c r="X54" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="X54" s="2" t="s">
+      <c r="Y54" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y54" s="2" t="s">
+      <c r="Z54" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="Z54" s="2" t="s">
+      <c r="AA54" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="AA54" s="2" t="s">
+      <c r="AB54" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB54" s="2" t="s">
+      <c r="AC54" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" ht="16.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>300</v>
       </c>
@@ -8570,60 +8894,63 @@
       <c r="J55" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K55" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="N55" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="O55" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="O55" s="2" t="s">
+      <c r="P55" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="P55" s="2" t="s">
+      <c r="Q55" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="Q55" s="2" t="s">
+      <c r="R55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R55" s="2" t="s">
+      <c r="S55" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S55" s="2" t="s">
+      <c r="T55" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="T55" s="2" t="s">
+      <c r="U55" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U55" s="2" t="s">
+      <c r="V55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V55" s="2"/>
-      <c r="W55" s="2" t="s">
+      <c r="W55" s="2"/>
+      <c r="X55" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X55" s="2" t="s">
+      <c r="Y55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y55" s="2" t="s">
+      <c r="Z55" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="Z55" s="2" t="s">
+      <c r="AA55" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="AA55" s="2" t="s">
+      <c r="AB55" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB55" s="2" t="s">
+      <c r="AC55" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>35</v>
       </c>
@@ -8654,60 +8981,63 @@
       <c r="J56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K56" t="s">
+        <v>1178</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="O56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O56" s="2" t="s">
+      <c r="P56" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P56" s="2" t="s">
+      <c r="Q56" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q56" s="2" t="s">
+      <c r="R56" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R56" s="2" t="s">
+      <c r="S56" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S56" s="2" t="s">
+      <c r="T56" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T56" s="2" t="s">
+      <c r="U56" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U56" s="2" t="s">
+      <c r="V56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V56" s="2"/>
-      <c r="W56" s="2" t="s">
+      <c r="W56" s="2"/>
+      <c r="X56" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X56" s="2" t="s">
+      <c r="Y56" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y56" s="2" t="s">
+      <c r="Z56" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="Z56" s="2" t="s">
+      <c r="AA56" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AA56" s="2" t="s">
+      <c r="AB56" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB56" s="2" t="s">
+      <c r="AC56" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>431</v>
       </c>
@@ -8738,62 +9068,65 @@
       <c r="J57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K57" s="2" t="s">
+      <c r="K57" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="O57" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="O57" s="2" t="s">
+      <c r="P57" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="P57" s="2" t="s">
+      <c r="Q57" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="Q57" s="2" t="s">
+      <c r="R57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R57" s="2" t="s">
+      <c r="S57" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S57" s="2" t="s">
+      <c r="T57" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="T57" s="2" t="s">
+      <c r="U57" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="U57" s="9" t="s">
+      <c r="V57" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V57" s="2" t="s">
+      <c r="W57" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W57" s="10" t="s">
+      <c r="X57" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X57" s="2" t="s">
+      <c r="Y57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y57" s="2" t="s">
+      <c r="Z57" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z57" s="2" t="s">
+      <c r="AA57" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="AA57" s="2" t="s">
+      <c r="AB57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB57" s="2" t="s">
+      <c r="AC57" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>66</v>
       </c>
@@ -8824,62 +9157,65 @@
       <c r="J58" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K58" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L58" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="N58" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="O58" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="O58" s="2" t="s">
+      <c r="P58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P58" s="2" t="s">
+      <c r="Q58" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="Q58" s="2" t="s">
+      <c r="R58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R58" s="2" t="s">
+      <c r="S58" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S58" s="2" t="s">
+      <c r="T58" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="T58" s="2" t="s">
+      <c r="U58" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U58" s="2" t="s">
+      <c r="V58" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V58" s="2" t="s">
+      <c r="W58" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W58" s="2" t="s">
+      <c r="X58" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="X58" s="2" t="s">
+      <c r="Y58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y58" s="2" t="s">
+      <c r="Z58" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z58" s="2" t="s">
+      <c r="AA58" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AA58" s="2" t="s">
+      <c r="AB58" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB58" s="2" t="s">
+      <c r="AC58" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>409</v>
       </c>
@@ -8910,62 +9246,65 @@
       <c r="J59" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="K59" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L59" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="M59" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="N59" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="O59" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="O59" s="2" t="s">
+      <c r="P59" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P59" s="2" t="s">
+      <c r="Q59" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="Q59" s="2" t="s">
+      <c r="R59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R59" s="2" t="s">
+      <c r="S59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="T59" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="T59" s="2" t="s">
+      <c r="U59" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="U59" s="9" t="s">
+      <c r="V59" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V59" s="2" t="s">
+      <c r="W59" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W59" s="2" t="s">
+      <c r="X59" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X59" s="2" t="s">
+      <c r="Y59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y59" s="2" t="s">
+      <c r="Z59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z59" s="2" t="s">
+      <c r="AA59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA59" s="2" t="s">
+      <c r="AB59" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="AB59" s="2" t="s">
+      <c r="AC59" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>345</v>
       </c>
@@ -8996,60 +9335,63 @@
       <c r="J60" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="K60" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L60" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L60" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="N60" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N60" s="2" t="s">
+      <c r="O60" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="O60" s="2" t="s">
+      <c r="P60" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P60" s="2" t="s">
+      <c r="Q60" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="Q60" s="2" t="s">
+      <c r="R60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R60" s="2" t="s">
+      <c r="S60" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S60" s="2" t="s">
+      <c r="T60" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T60" s="2" t="s">
+      <c r="U60" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="U60" s="2" t="s">
+      <c r="V60" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V60" s="2"/>
-      <c r="W60" s="2" t="s">
+      <c r="W60" s="2"/>
+      <c r="X60" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X60" s="2" t="s">
+      <c r="Y60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y60" s="2" t="s">
+      <c r="Z60" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Z60" s="2" t="s">
+      <c r="AA60" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AA60" s="2" t="s">
+      <c r="AB60" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB60" s="2" t="s">
+      <c r="AC60" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>275</v>
       </c>
@@ -9080,60 +9422,63 @@
       <c r="J61" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="K61" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L61" s="2" t="s">
+      <c r="M61" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="N61" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N61" s="2" t="s">
+      <c r="O61" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="O61" s="2" t="s">
+      <c r="P61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P61" s="2" t="s">
+      <c r="Q61" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="Q61" s="2" t="s">
+      <c r="R61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R61" s="2" t="s">
+      <c r="S61" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="S61" s="2" t="s">
+      <c r="T61" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T61" s="2" t="s">
+      <c r="U61" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="U61" s="2" t="s">
+      <c r="V61" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V61" s="2"/>
-      <c r="W61" s="10" t="s">
+      <c r="W61" s="2"/>
+      <c r="X61" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X61" s="2" t="s">
+      <c r="Y61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y61" s="2" t="s">
+      <c r="Z61" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z61" s="2" t="s">
+      <c r="AA61" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA61" s="2" t="s">
+      <c r="AB61" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AB61" s="2" t="s">
+      <c r="AC61" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>444</v>
       </c>
@@ -9164,62 +9509,65 @@
       <c r="J62" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K62" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L62" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="M62" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="N62" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N62" s="2" t="s">
+      <c r="O62" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="P62" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="Q62" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="Q62" s="2" t="s">
+      <c r="R62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R62" s="2" t="s">
+      <c r="S62" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="S62" s="2" t="s">
+      <c r="T62" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="T62" s="2" t="s">
+      <c r="U62" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="U62" s="9" t="s">
+      <c r="V62" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V62" s="2" t="s">
+      <c r="W62" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W62" s="2" t="s">
+      <c r="X62" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X62" s="2" t="s">
+      <c r="Y62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y62" s="2" t="s">
+      <c r="Z62" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z62" s="2" t="s">
+      <c r="AA62" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="AA62" s="2" t="s">
+      <c r="AB62" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB62" s="2" t="s">
+      <c r="AC62" s="2" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>331</v>
       </c>
@@ -9250,58 +9598,61 @@
       <c r="J63" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="K63" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L63" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="L63" s="2" t="s">
+      <c r="M63" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="N63" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="N63" s="2" t="s">
+      <c r="O63" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O63" s="2" t="s">
+      <c r="P63" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P63" s="2" t="s">
+      <c r="Q63" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="Q63" s="2" t="s">
+      <c r="R63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R63" s="2" t="s">
+      <c r="S63" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2" t="s">
+      <c r="T63" s="2"/>
+      <c r="U63" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="U63" s="2" t="s">
+      <c r="V63" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V63" s="2"/>
-      <c r="W63" s="2" t="s">
+      <c r="W63" s="2"/>
+      <c r="X63" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="X63" s="2" t="s">
+      <c r="Y63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y63" s="2" t="s">
+      <c r="Z63" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="Z63" s="2" t="s">
+      <c r="AA63" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="AA63" s="2" t="s">
+      <c r="AB63" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="AB63" s="2" t="s">
+      <c r="AC63" s="2" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" ht="16.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>607</v>
       </c>
@@ -9332,58 +9683,61 @@
       <c r="J64" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K64" s="2" t="s">
+      <c r="K64" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L64" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L64" s="2" t="s">
+      <c r="M64" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="N64" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N64" s="2" t="s">
+      <c r="O64" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O64" s="2" t="s">
+      <c r="P64" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P64" s="2" t="s">
+      <c r="Q64" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="Q64" s="2" t="s">
+      <c r="R64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R64" s="2" t="s">
+      <c r="S64" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="S64" s="2" t="s">
+      <c r="T64" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="T64" s="2" t="s">
+      <c r="U64" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="U64" s="2" t="s">
+      <c r="V64" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V64" s="2"/>
-      <c r="W64" s="2" t="s">
+      <c r="W64" s="2"/>
+      <c r="X64" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X64" s="2" t="s">
+      <c r="Y64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y64" s="2" t="s">
+      <c r="Z64" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z64" s="2" t="s">
+      <c r="AA64" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="AA64" s="2"/>
-      <c r="AB64" s="2" t="s">
+      <c r="AB64" s="2"/>
+      <c r="AC64" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>112</v>
       </c>
@@ -9412,60 +9766,63 @@
       <c r="J65" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="K65" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L65" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L65" s="2" t="s">
+      <c r="M65" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="N65" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N65" s="2" t="s">
+      <c r="O65" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O65" s="2" t="s">
+      <c r="P65" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P65" s="2" t="s">
+      <c r="Q65" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="Q65" s="2" t="s">
+      <c r="R65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R65" s="2" t="s">
+      <c r="S65" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="S65" s="2" t="s">
+      <c r="T65" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="T65" s="2" t="s">
+      <c r="U65" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="U65" s="2" t="s">
+      <c r="V65" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V65" s="2"/>
-      <c r="W65" s="2" t="s">
+      <c r="W65" s="2"/>
+      <c r="X65" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X65" s="2" t="s">
+      <c r="Y65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y65" s="2" t="s">
+      <c r="Z65" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="Z65" s="12" t="s">
+      <c r="AA65" s="12" t="s">
         <v>719</v>
       </c>
-      <c r="AA65" s="2" t="s">
+      <c r="AB65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB65" s="2" t="s">
+      <c r="AC65" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>190</v>
       </c>
@@ -9494,60 +9851,63 @@
       <c r="J66" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="K66" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L66" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L66" s="2" t="s">
+      <c r="M66" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="N66" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N66" s="2" t="s">
+      <c r="O66" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="O66" s="2" t="s">
+      <c r="P66" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P66" s="2" t="s">
+      <c r="Q66" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="Q66" s="2" t="s">
+      <c r="R66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R66" s="2" t="s">
+      <c r="S66" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S66" s="2" t="s">
+      <c r="T66" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="T66" s="2" t="s">
+      <c r="U66" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="U66" s="2" t="s">
+      <c r="V66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V66" s="2"/>
-      <c r="W66" s="10" t="s">
+      <c r="W66" s="2"/>
+      <c r="X66" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X66" s="2" t="s">
+      <c r="Y66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y66" s="2" t="s">
+      <c r="Z66" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="Z66" s="2" t="s">
+      <c r="AA66" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="AA66" s="2" t="s">
+      <c r="AB66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB66" s="2" t="s">
+      <c r="AC66" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>83</v>
       </c>
@@ -9578,60 +9938,63 @@
       <c r="J67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="K67" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L67" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L67" s="9" t="s">
+      <c r="M67" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="N67" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N67" s="2" t="s">
+      <c r="O67" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="O67" s="2" t="s">
+      <c r="P67" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="P67" s="2" t="s">
+      <c r="Q67" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="Q67" s="2" t="s">
+      <c r="R67" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R67" s="2" t="s">
+      <c r="S67" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="T67" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="T67" s="2" t="s">
+      <c r="U67" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="U67" s="2" t="s">
+      <c r="V67" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V67" s="2"/>
-      <c r="W67" s="10" t="s">
+      <c r="W67" s="2"/>
+      <c r="X67" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X67" s="2" t="s">
+      <c r="Y67" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y67" s="2" t="s">
+      <c r="Z67" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z67" s="2" t="s">
+      <c r="AA67" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="AA67" s="2" t="s">
+      <c r="AB67" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="AB67" s="2" t="s">
+      <c r="AC67" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" ht="16.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>230</v>
       </c>
@@ -9660,60 +10023,63 @@
       <c r="J68" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="K68" t="s">
+        <v>1185</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="N68" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N68" s="2" t="s">
+      <c r="O68" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="O68" s="2" t="s">
+      <c r="P68" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P68" s="2" t="s">
+      <c r="Q68" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="Q68" s="2" t="s">
+      <c r="R68" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R68" s="2" t="s">
+      <c r="S68" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="T68" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="T68" s="2" t="s">
+      <c r="U68" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="U68" s="2" t="s">
+      <c r="V68" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2" t="s">
+      <c r="W68" s="2"/>
+      <c r="X68" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="X68" s="2" t="s">
+      <c r="Y68" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y68" s="2" t="s">
+      <c r="Z68" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="Z68" s="2" t="s">
+      <c r="AA68" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="AA68" s="2" t="s">
+      <c r="AB68" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB68" s="2" t="s">
+      <c r="AC68" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
@@ -9744,62 +10110,65 @@
       <c r="J69" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K69" s="9" t="s">
+      <c r="K69" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="L69" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L69" s="2" t="s">
+      <c r="M69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="N69" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N69" s="2" t="s">
+      <c r="O69" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O69" s="2" t="s">
+      <c r="P69" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P69" s="9" t="s">
+      <c r="Q69" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q69" s="2" t="s">
+      <c r="R69" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R69" s="11" t="s">
+      <c r="S69" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S69" s="2" t="s">
+      <c r="T69" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T69" s="2" t="s">
+      <c r="U69" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U69" s="2" t="s">
+      <c r="V69" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V69" s="9" t="s">
+      <c r="W69" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W69" s="2" t="s">
+      <c r="X69" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X69" s="2" t="s">
+      <c r="Y69" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y69" s="2" t="s">
+      <c r="Z69" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z69" s="2" t="s">
+      <c r="AA69" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA69" s="2" t="s">
+      <c r="AB69" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AB69" s="2" t="s">
+      <c r="AC69" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>24</v>
       </c>
@@ -9828,62 +10197,65 @@
       <c r="J70" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="K70" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L70" s="2" t="s">
+      <c r="M70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="N70" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N70" s="2" t="s">
+      <c r="O70" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O70" s="2" t="s">
+      <c r="P70" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P70" s="2" t="s">
+      <c r="Q70" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q70" s="2" t="s">
+      <c r="R70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R70" s="2" t="s">
+      <c r="S70" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S70" s="11" t="s">
+      <c r="T70" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="T70" s="2" t="s">
+      <c r="U70" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U70" s="2" t="s">
+      <c r="V70" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V70" s="9" t="s">
+      <c r="W70" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W70" s="10" t="s">
+      <c r="X70" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X70" s="2" t="s">
+      <c r="Y70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y70" s="2" t="s">
+      <c r="Z70" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="Z70" s="2" t="s">
+      <c r="AA70" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AA70" s="2" t="s">
+      <c r="AB70" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB70" s="2" t="s">
+      <c r="AC70" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>474</v>
       </c>
@@ -9914,62 +10286,65 @@
       <c r="J71" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="K71" s="2" t="s">
+      <c r="K71" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L71" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L71" s="2" t="s">
+      <c r="M71" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M71" s="2" t="s">
+      <c r="N71" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N71" s="2" t="s">
+      <c r="O71" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="O71" s="2" t="s">
+      <c r="P71" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P71" s="2" t="s">
+      <c r="Q71" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="Q71" s="2" t="s">
+      <c r="R71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R71" s="2" t="s">
+      <c r="S71" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="S71" s="2" t="s">
+      <c r="T71" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="T71" s="2" t="s">
+      <c r="U71" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="U71" s="9" t="s">
+      <c r="V71" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="V71" s="2" t="s">
+      <c r="W71" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W71" s="2" t="s">
+      <c r="X71" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X71" s="2" t="s">
+      <c r="Y71" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y71" s="2" t="s">
+      <c r="Z71" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z71" s="2" t="s">
+      <c r="AA71" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="AA71" s="2" t="s">
+      <c r="AB71" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB71" s="2" t="s">
+      <c r="AC71" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>133</v>
       </c>
@@ -10000,60 +10375,63 @@
       <c r="J72" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="K72" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L72" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L72" s="2" t="s">
+      <c r="M72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M72" s="2" t="s">
+      <c r="N72" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N72" s="2" t="s">
+      <c r="O72" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="O72" s="2" t="s">
+      <c r="P72" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P72" s="2" t="s">
+      <c r="Q72" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Q72" s="2" t="s">
+      <c r="R72" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="R72" s="2" t="s">
+      <c r="S72" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S72" s="2" t="s">
+      <c r="T72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T72" s="2" t="s">
+      <c r="U72" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="U72" s="2" t="s">
+      <c r="V72" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2" t="s">
+      <c r="W72" s="2"/>
+      <c r="X72" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X72" s="2" t="s">
+      <c r="Y72" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y72" s="2" t="s">
+      <c r="Z72" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="Z72" s="2" t="s">
+      <c r="AA72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="AA72" s="2" t="s">
+      <c r="AB72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB72" s="2" t="s">
+      <c r="AC72" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>492</v>
       </c>
@@ -10084,62 +10462,65 @@
       <c r="J73" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="K73" t="s">
+        <v>1188</v>
+      </c>
+      <c r="L73" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L73" s="2" t="s">
+      <c r="M73" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M73" s="2" t="s">
+      <c r="N73" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N73" s="2" t="s">
+      <c r="O73" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="O73" s="2" t="s">
+      <c r="P73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P73" s="2" t="s">
+      <c r="Q73" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="Q73" s="2" t="s">
+      <c r="R73" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R73" s="2" t="s">
+      <c r="S73" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="S73" s="2" t="s">
+      <c r="T73" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="T73" s="2" t="s">
+      <c r="U73" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="U73" s="9" t="s">
+      <c r="V73" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V73" s="2" t="s">
+      <c r="W73" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W73" s="2" t="s">
+      <c r="X73" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="X73" s="2" t="s">
+      <c r="Y73" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y73" s="2" t="s">
+      <c r="Z73" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="Z73" s="2" t="s">
+      <c r="AA73" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="AA73" s="2" t="s">
+      <c r="AB73" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="AB73" s="2" t="s">
+      <c r="AC73" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>526</v>
       </c>
@@ -10170,60 +10551,63 @@
       <c r="J74" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="K74" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L74" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L74" s="2" t="s">
+      <c r="M74" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M74" s="2" t="s">
+      <c r="N74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N74" s="2" t="s">
+      <c r="O74" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="O74" s="2" t="s">
+      <c r="P74" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P74" s="2" t="s">
+      <c r="Q74" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="Q74" s="2" t="s">
+      <c r="R74" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R74" s="2" t="s">
+      <c r="S74" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S74" s="2" t="s">
+      <c r="T74" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="T74" s="2" t="s">
+      <c r="U74" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="U74" s="2" t="s">
+      <c r="V74" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V74" s="2"/>
-      <c r="W74" s="2" t="s">
+      <c r="W74" s="2"/>
+      <c r="X74" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="X74" s="2" t="s">
+      <c r="Y74" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y74" s="2" t="s">
+      <c r="Z74" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="Z74" s="2" t="s">
+      <c r="AA74" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="AA74" s="2" t="s">
+      <c r="AB74" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB74" s="2" t="s">
+      <c r="AC74" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="75" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>206</v>
       </c>
@@ -10254,58 +10638,61 @@
       <c r="J75" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="K75" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L75" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L75" s="2" t="s">
+      <c r="M75" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M75" s="2" t="s">
+      <c r="N75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N75" s="2" t="s">
+      <c r="O75" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="O75" s="2" t="s">
+      <c r="P75" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P75" s="2" t="s">
+      <c r="Q75" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="Q75" s="2" t="s">
+      <c r="R75" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R75" s="2" t="s">
+      <c r="S75" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S75" s="2" t="s">
+      <c r="T75" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="T75" s="2" t="s">
+      <c r="U75" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U75" s="2" t="s">
+      <c r="V75" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2" t="s">
+      <c r="W75" s="2"/>
+      <c r="X75" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="X75" s="2" t="s">
+      <c r="Y75" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y75" s="2" t="s">
+      <c r="Z75" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="Z75" s="2" t="s">
+      <c r="AA75" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AA75" s="2"/>
-      <c r="AB75" s="2" t="s">
+      <c r="AB75" s="2"/>
+      <c r="AC75" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="76" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
         <v>615</v>
       </c>
@@ -10336,58 +10723,61 @@
       <c r="J76" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K76" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L76" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L76" s="2" t="s">
+      <c r="M76" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M76" s="2" t="s">
+      <c r="N76" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N76" s="2" t="s">
+      <c r="O76" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O76" s="2" t="s">
+      <c r="P76" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P76" s="2" t="s">
+      <c r="Q76" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="Q76" s="2" t="s">
+      <c r="R76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R76" s="2" t="s">
+      <c r="S76" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="S76" s="2" t="s">
+      <c r="T76" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="T76" s="2" t="s">
+      <c r="U76" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="U76" s="2" t="s">
+      <c r="V76" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2" t="s">
+      <c r="W76" s="2"/>
+      <c r="X76" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="X76" s="2" t="s">
+      <c r="Y76" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y76" s="2" t="s">
+      <c r="Z76" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="Z76" s="2" t="s">
+      <c r="AA76" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="AA76" s="2"/>
-      <c r="AB76" s="2" t="s">
+      <c r="AB76" s="2"/>
+      <c r="AC76" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="77" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>267</v>
       </c>
@@ -10416,75 +10806,78 @@
       <c r="J77" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="K77" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L77" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L77" s="2" t="s">
+      <c r="M77" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="N77" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N77" s="2" t="s">
+      <c r="O77" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="O77" s="2" t="s">
+      <c r="P77" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P77" s="2" t="s">
+      <c r="Q77" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="Q77" s="2" t="s">
+      <c r="R77" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R77" s="2" t="s">
+      <c r="S77" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S77" s="2" t="s">
+      <c r="T77" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T77" s="2" t="s">
+      <c r="U77" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="U77" s="2" t="s">
+      <c r="V77" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V77" s="2"/>
-      <c r="W77" s="10" t="s">
+      <c r="W77" s="2"/>
+      <c r="X77" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="X77" s="2" t="s">
+      <c r="Y77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y77" s="2" t="s">
+      <c r="Z77" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="Z77" s="2" t="s">
+      <c r="AA77" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AA77" s="2" t="s">
+      <c r="AB77" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AB77" s="2" t="s">
+      <c r="AC77" s="2" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="79" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W79" s="1"/>
+    <row r="79" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="X79" s="1"/>
     </row>
-    <row r="81" spans="23:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="W81" s="1"/>
+    <row r="81" spans="24:24" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="X81" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA81">
-    <sortCondition ref="T1:T81"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB81">
+    <sortCondition ref="U1:U81"/>
   </sortState>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q9" xr:uid="{63F3FD65-0125-45EA-AE78-F52CED541A5E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R9" xr:uid="{63F3FD65-0125-45EA-AE78-F52CED541A5E}">
       <formula1>"Quantitative, Qualitative, Other"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z6 U19 AA74:AA1048576 AA72 Z74 AA44 Z45 AA46:AA48 Z49 AA50 AA52:AA59 Z51 AA61:AA62 Z63:Z64 Z76:Z78 Z80:Z1048576 M46:M54 AA32:AA42 K17:K32 K1:M16 Z7:AA31 Z33:Z43 K34:K43 Z1:AA5 Z65:AA71 L17:M43 K44:L54 K55:M1048576" xr:uid="{35419BFC-1E57-4C54-8DC8-4D9B914213A1}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V44:V64" xr:uid="{2DDB7440-D7A5-488A-B2DB-396EE478CDFE}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA6 V19 AB74:AB1048576 AB72 AA74 AB44 AA45 AB46:AB48 AA49 AB50 AB52:AB59 AA51 AB61:AB62 AA63:AA64 AA76:AA78 AA80:AA1048576 N46:N54 AB32:AB42 L17:L32 L1:N16 AA7:AB31 AA33:AA43 L34:L43 AA1:AB5 AA65:AB71 M17:N43 L44:M54 L55:N1048576" xr:uid="{35419BFC-1E57-4C54-8DC8-4D9B914213A1}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W44:W64" xr:uid="{2DDB7440-D7A5-488A-B2DB-396EE478CDFE}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
